--- a/data/inventory.xlsx
+++ b/data/inventory.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InventoryData" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="InventoryData" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,14 +16,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +48,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,81 +429,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ItemID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ItemName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>DateAdded</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>LastUpdated</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ModelNumber</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SerialNumber</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>WarrantyExpiration</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>WarrantyProvider</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>AlertSent</t>
         </is>
@@ -501,7 +517,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lenovo Monitor 1</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -517,15 +533,11 @@
           <t>Main Office</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2024-12-08</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2025-03-08</t>
-        </is>
+      <c r="F2" s="2" t="n">
+        <v>45634</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -550,10 +562,8 @@
           <t>Retired</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
+      <c r="M2" s="2" t="n">
+        <v>46223</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -569,17 +579,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ITM0002</t>
+          <t>ITM0003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cisco Printer 2</t>
+          <t>Lenovo Laptop 3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Printer</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -587,50 +597,44 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
+          <t>Warehouse B</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>45539</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CI-2547</t>
+          <t>LE-7685</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>SN13752884</t>
+          <t>SN97026474</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>354.3</v>
+        <v>1568.69</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
+      <c r="M3" s="2" t="n">
+        <v>46367</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -642,36 +646,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ITM0003</t>
+          <t>ITM0004</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lenovo Laptop 3</t>
+          <t>Lenovo Printer 4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Warehouse B</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2024-09-04</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2024-11-24</t>
-        </is>
+      <c r="F4" s="2" t="n">
+        <v>45542</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -680,30 +680,28 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LE-7685</t>
+          <t>LE-1836</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SN97026474</t>
+          <t>SN13646074</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1568.69</v>
+        <v>2408.84</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-12-11</t>
-        </is>
+          <t>In Repair</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>46072</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -715,68 +713,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ITM0004</t>
+          <t>ITM0005</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lenovo Printer 4</t>
+          <t>Cisco Tablet 5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Printer</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Warehouse B</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2024-09-07</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2024-10-13</t>
-        </is>
+          <t>Main Office</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>45544</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LE-1836</t>
+          <t>CI-2350</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>SN13646074</t>
+          <t>SN69836053</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2408.84</v>
+        <v>313.09</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
+      <c r="M5" s="2" t="n">
+        <v>45945</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>AppleCare</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -788,36 +780,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ITM0005</t>
+          <t>ITM0006</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cisco Tablet 5</t>
+          <t>Cisco Printer 6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Main Office</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2024-12-24</t>
-        </is>
+          <t>Warehouse A</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>45559</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -826,30 +814,28 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CI-2350</t>
+          <t>CI-6701</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SN69836053</t>
+          <t>SN12947104</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>313.09</v>
+        <v>1687.5</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>46071</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>AppleCare</t>
+          <t>Dell Support</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -861,109 +847,99 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ITM0006</t>
+          <t>ITM0007</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cisco Printer 6</t>
+          <t>Dell Switch 7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Printer</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2024-09-25</t>
-        </is>
+          <t>Remote Site</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>45525</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Dell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CI-6701</t>
+          <t>DE-2415</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>SN12947104</t>
+          <t>SN87049713</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1687.5</v>
+        <v>2370.61</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>46200</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Dell Support</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ITM0007</t>
+          <t>ITM0008</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dell Switch 7</t>
+          <t>Dell Laptop 8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Remote Site</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2024-12-07</t>
-        </is>
+          <t>Warehouse A</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>45489</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -972,47 +948,45 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DE-2415</t>
+          <t>DE-1712</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>SN87049713</t>
+          <t>SN18103129</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2370.61</v>
+        <v>2180.61</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
+      <c r="M8" s="2" t="n">
+        <v>46378</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>Lenovo Premium</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ITM0008</t>
+          <t>ITM0009</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dell Laptop 8</t>
+          <t>Lenovo Laptop 9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1021,196 +995,178 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2024-07-25</t>
-        </is>
+          <t>Remote Site</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>45538</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Dell</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DE-1712</t>
+          <t>LE-1750</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SN18103129</t>
+          <t>SN74709854</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2180.61</v>
+        <v>236.03</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Retired</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2026-12-22</t>
-        </is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>46306</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Lenovo Premium</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ITM0009</t>
+          <t>ITM0010</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lenovo Laptop 9</t>
+          <t>Epson Switch 10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Remote Site</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2024-09-03</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2025-02-08</t>
-        </is>
+          <t>Main Office</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>45482</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LE-1750</t>
+          <t>EP-4082</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>SN74709854</t>
+          <t>SN34126567</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>236.03</v>
+        <v>164.94</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
+          <t>In Repair</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>46095</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>Dell Support</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ITM0010</t>
+          <t>ITM0011</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Epson Switch 10</t>
+          <t>Cisco Tablet 11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Main Office</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2024-10-16</t>
-        </is>
+      <c r="F11" s="2" t="n">
+        <v>45357</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>EP-4082</t>
+          <t>CI-2186</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SN34126567</t>
+          <t>SN68308926</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>164.94</v>
+        <v>1459.56</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>45811</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1226,68 +1182,62 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ITM0011</t>
+          <t>ITM0012</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cisco Tablet 11</t>
+          <t>Epson Laptop 12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Main Office</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2024-06-23</t>
-        </is>
+          <t>Warehouse A</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>45558</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CI-2186</t>
+          <t>EP-7148</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SN68308926</t>
+          <t>SN46504782</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1459.56</v>
+        <v>436.06</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-06-03</t>
-        </is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>46076</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Dell Support</t>
+          <t>AppleCare</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1299,141 +1249,129 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ITM0012</t>
+          <t>ITM0013</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Epson Laptop 12</t>
+          <t>Cisco Switch 13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2024-12-25</t>
-        </is>
+          <t>Warehouse B</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>45470</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>EP-7148</t>
+          <t>CI-2801</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SN46504782</t>
+          <t>SN53129241</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>436.06</v>
+        <v>373.47</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
+      <c r="M13" s="2" t="n">
+        <v>46484</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>AppleCare</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ITM0013</t>
+          <t>ITM0014</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cisco Switch 13</t>
+          <t>Epson Laptop 14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Warehouse B</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2024-10-31</t>
-        </is>
+          <t>Warehouse A</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>45349</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CI-2801</t>
+          <t>EP-5617</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SN53129241</t>
+          <t>SN55743232</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>373.47</v>
+        <v>735.75</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Retired</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2027-04-07</t>
-        </is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>46372</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>Dell Support</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1445,64 +1383,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ITM0014</t>
+          <t>ITM0015</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Epson Laptop 14</t>
+          <t>Cisco Tablet 15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2024-02-27</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
+      <c r="F15" s="2" t="n">
+        <v>45473</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>EP-5617</t>
+          <t>CI-2377</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SN55743232</t>
+          <t>SN20908357</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>735.75</v>
+        <v>1139.36</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
+          <t>In Repair</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>45876</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1511,144 +1443,132 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ITM0015</t>
+          <t>ITM0016</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cisco Tablet 15</t>
+          <t>Lenovo Switch 16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
+          <t>Remote Site</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>45327</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CI-2377</t>
+          <t>LE-4738</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>SN20908357</t>
+          <t>SN48992827</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1139.36</v>
+        <v>1092.84</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>45963</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Dell Support</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ITM0016</t>
+          <t>ITM0017</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lenovo Switch 16</t>
+          <t>Apple Laptop 17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>Remote Site</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2024-02-05</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2024-07-25</t>
-        </is>
+      <c r="F17" s="2" t="n">
+        <v>45346</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>LE-4738</t>
+          <t>AP-7166</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>SN48992827</t>
+          <t>SN96842624</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1092.84</v>
+        <v>474.43</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Retired</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-11-02</t>
-        </is>
+          <t>In Repair</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>46011</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1657,144 +1577,132 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ITM0017</t>
+          <t>ITM0018</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Apple Laptop 17</t>
+          <t>Cisco Printer 18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Remote Site</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2024-02-24</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
+          <t>Warehouse A</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>45423</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AP-7166</t>
+          <t>CI-5274</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SN96842624</t>
+          <t>SN32000764</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>474.43</v>
+        <v>2180.93</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
+      <c r="M18" s="2" t="n">
+        <v>45901</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>AppleCare</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ITM0018</t>
+          <t>ITM0019</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cisco Printer 18</t>
+          <t>Epson Switch 19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Printer</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2024-05-11</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2024-10-11</t>
-        </is>
+          <t>Warehouse B</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>45347</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CI-5274</t>
+          <t>EP-9652</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SN32000764</t>
+          <t>SN57657634</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2180.93</v>
+        <v>557.09</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>46137</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1810,17 +1718,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ITM0019</t>
+          <t>ITM0020</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Epson Switch 19</t>
+          <t>Epson Monitor 20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1828,18 +1736,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Warehouse B</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2024-02-25</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2024-04-18</t>
-        </is>
+          <t>Main Office</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>45632</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1848,26 +1752,24 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>EP-9652</t>
+          <t>EP-3391</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SN57657634</t>
+          <t>SN80990521</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>557.09</v>
+        <v>1575.15</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Retired</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>46267</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1876,75 +1778,69 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ITM0020</t>
+          <t>ITM0021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Epson Monitor 20</t>
+          <t>Apple Laptop 21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Main Office</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2025-02-10</t>
-        </is>
+          <t>IT Closet</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>45492</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>EP-3391</t>
+          <t>AP-6473</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SN80990521</t>
+          <t>SN43317146</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1575.15</v>
+        <v>2389.73</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
+          <t>In Repair</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>45897</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>AppleCare</t>
+          <t>Lenovo Premium</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1956,141 +1852,129 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ITM0021</t>
+          <t>ITM0022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Apple Laptop 21</t>
+          <t>Dell Printer 22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IT Closet</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2024-07-19</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2024-10-23</t>
-        </is>
+          <t>Remote Site</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>45592</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Dell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AP-6473</t>
+          <t>DE-4929</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SN43317146</t>
+          <t>SN87250266</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>2389.73</v>
+        <v>997.01</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>46371</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Lenovo Premium</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ITM0022</t>
+          <t>ITM0023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dell Printer 22</t>
+          <t>Apple Switch 23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Printer</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Remote Site</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2024-10-27</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2025-03-11</t>
-        </is>
+          <t>Warehouse A</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>45434</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Dell</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DE-4929</t>
+          <t>AP-9603</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>SN87250266</t>
+          <t>SN95175226</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>997.01</v>
+        <v>661.0599999999999</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Retired</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>46449</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>AppleCare</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2102,36 +1986,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ITM0023</t>
+          <t>ITM0024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Apple Switch 23</t>
+          <t>Apple Tablet 24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2024-05-22</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
+      <c r="F24" s="2" t="n">
+        <v>45632</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2140,30 +2020,28 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AP-9603</t>
+          <t>AP-7433</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SN95175226</t>
+          <t>SN76849184</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>661.0599999999999</v>
+        <v>1246.48</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2027-03-03</t>
-        </is>
+          <t>In Repair</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>46662</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>AppleCare</t>
+          <t>Dell Support</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2175,68 +2053,62 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ITM0024</t>
+          <t>ITM0025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Apple Tablet 24</t>
+          <t>Epson Switch 25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2025-04-30</t>
-        </is>
+          <t>IT Closet</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>45644</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AP-7433</t>
+          <t>EP-4607</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SN76849184</t>
+          <t>SN31564647</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1246.48</v>
+        <v>1661.51</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2027-10-02</t>
-        </is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>46089</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Dell Support</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2248,12 +2120,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ITM0025</t>
+          <t>ITM0026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Epson Switch 25</t>
+          <t>Epson Switch 26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2262,22 +2134,18 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IT Closet</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2025-01-16</t>
-        </is>
+          <t>Warehouse A</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2286,30 +2154,28 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>EP-4607</t>
+          <t>EP-9269</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SN31564647</t>
+          <t>SN21333025</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1661.51</v>
+        <v>2350.61</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Retired</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>46080</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>AppleCare</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2321,182 +2187,166 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ITM0026</t>
+          <t>ITM0027</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Epson Switch 26</t>
+          <t>Dell Router 27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2024-10-21</t>
-        </is>
+          <t>Main Office</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>45418</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Dell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>EP-9269</t>
+          <t>DE-1340</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SN21333025</t>
+          <t>SN27521419</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2350.61</v>
+        <v>2205.55</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
+          <t>In Repair</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>45947</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>AppleCare</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ITM0027</t>
+          <t>ITM0028</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dell Router 27</t>
+          <t>Epson Laptop 28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>Main Office</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2024-10-29</t>
-        </is>
+      <c r="F28" s="2" t="n">
+        <v>45321</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Dell</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>DE-1340</t>
+          <t>EP-9395</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SN27521419</t>
+          <t>SN97552808</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>2205.55</v>
+        <v>2482.81</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>46070</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>Dell Support</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ITM0028</t>
+          <t>ITM0029</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Epson Laptop 28</t>
+          <t>Epson Tablet 29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Main Office</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2024-01-30</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2024-04-27</t>
-        </is>
+          <t>IT Closet</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>45419</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2505,30 +2355,28 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>EP-9395</t>
+          <t>EP-1066</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SN97552808</t>
+          <t>SN93333985</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>2482.81</v>
+        <v>950.09</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Retired</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
+          <t>In Repair</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>45832</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Dell Support</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2540,64 +2388,58 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ITM0029</t>
+          <t>ITM0030</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Epson Tablet 29</t>
+          <t>HP Laptop 30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>IT Closet</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2024-10-08</t>
-        </is>
+      <c r="F30" s="2" t="n">
+        <v>45293</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EP-1066</t>
+          <t>HP-4733</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SN93333985</t>
+          <t>SN34742385</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>950.09</v>
+        <v>2499.3</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2025-06-24</t>
-        </is>
+      <c r="M30" s="2" t="n">
+        <v>45875</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2606,24 +2448,24 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ITM0030</t>
+          <t>ITM0031</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HP Laptop 30</t>
+          <t>HP Router 31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -2634,15 +2476,11 @@
           <t>IT Closet</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2024-01-02</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2024-06-05</t>
-        </is>
+      <c r="F31" s="2" t="n">
+        <v>45416</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2651,30 +2489,28 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>HP-4733</t>
+          <t>HP-8118</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SN34742385</t>
+          <t>SN69731506</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>2499.3</v>
+        <v>166.49</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2025-08-06</t>
-        </is>
+      <c r="M31" s="2" t="n">
+        <v>46282</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>Lenovo Premium</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2686,64 +2522,58 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ITM0031</t>
+          <t>ITM0032</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HP Router 31</t>
+          <t>Epson Laptop 32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IT Closet</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2024-08-02</t>
-        </is>
+          <t>Warehouse B</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>45445</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>HP-8118</t>
+          <t>EP-6464</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SN69731506</t>
+          <t>SN29099365</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>166.49</v>
+        <v>1136.78</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
+      <c r="M32" s="2" t="n">
+        <v>46024</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2752,75 +2582,69 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ITM0032</t>
+          <t>ITM0033</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Epson Laptop 32</t>
+          <t>Dell Printer 33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>Warehouse B</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2024-06-02</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2024-09-18</t>
-        </is>
+      <c r="F33" s="2" t="n">
+        <v>45550</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Dell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>EP-6464</t>
+          <t>DE-1295</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SN29099365</t>
+          <t>SN68145944</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1136.78</v>
+        <v>408.32</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>46031</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Lenovo Premium</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2832,68 +2656,62 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ITM0033</t>
+          <t>ITM0034</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dell Printer 33</t>
+          <t>Epson Monitor 34</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Printer</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>Warehouse B</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2024-09-15</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2025-02-22</t>
-        </is>
+      <c r="F34" s="2" t="n">
+        <v>45569</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Dell</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DE-1295</t>
+          <t>EP-5669</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>SN68145944</t>
+          <t>SN26610527</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>408.32</v>
+        <v>1599.97</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2026-01-09</t>
-        </is>
+      <c r="M34" s="2" t="n">
+        <v>46114</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2905,85 +2723,79 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ITM0034</t>
+          <t>ITM0035</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Epson Monitor 34</t>
+          <t>Cisco Switch 35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Warehouse B</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2024-11-18</t>
-        </is>
+          <t>Warehouse A</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>45363</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>EP-5669</t>
+          <t>CI-6537</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>SN26610527</t>
+          <t>SN80427769</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1599.97</v>
+        <v>1109.75</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>45976</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>Lenovo Premium</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ITM0035</t>
+          <t>ITM0036</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cisco Switch 35</t>
+          <t>Epson Switch 36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2992,54 +2804,48 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2024-03-12</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2024-07-16</t>
-        </is>
+      <c r="F36" s="2" t="n">
+        <v>45354</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>CI-6537</t>
+          <t>EP-1758</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>SN80427769</t>
+          <t>SN53690854</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1109.75</v>
+        <v>2216.96</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Retired</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>2025-11-15</t>
-        </is>
+          <t>In Repair</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>45776</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Lenovo Premium</t>
+          <t>AppleCare</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3051,68 +2857,62 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ITM0036</t>
+          <t>ITM0037</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Epson Switch 36</t>
+          <t>Apple Monitor 37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2024-07-07</t>
-        </is>
+          <t>Remote Site</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>45343</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>EP-1758</t>
+          <t>AP-9201</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SN53690854</t>
+          <t>SN54771677</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>2216.96</v>
+        <v>1068.81</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2025-04-29</t>
-        </is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>45840</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>AppleCare</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3124,68 +2924,62 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ITM0037</t>
+          <t>ITM0038</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Apple Monitor 37</t>
+          <t>Epson Router 38</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Remote Site</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2024-02-21</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2024-07-04</t>
-        </is>
+          <t>IT Closet</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>45529</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AP-9201</t>
+          <t>EP-7936</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SN54771677</t>
+          <t>SN38050053</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1068.81</v>
+        <v>511.93</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
+          <t>In Repair</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>46438</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3197,68 +2991,62 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ITM0038</t>
+          <t>ITM0039</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Epson Router 38</t>
+          <t>HP Monitor 39</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IT Closet</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2024-12-22</t>
-        </is>
+          <t>Remote Site</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>45345</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EP-7936</t>
+          <t>HP-6900</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SN38050053</t>
+          <t>SN21882986</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>511.93</v>
+        <v>1370.66</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2027-02-20</t>
-        </is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>45947</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3270,12 +3058,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ITM0039</t>
+          <t>ITM0040</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HP Monitor 39</t>
+          <t>Epson Monitor 40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3284,71 +3072,65 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Remote Site</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2024-02-23</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2024-07-29</t>
-        </is>
+          <t>Warehouse A</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>45646</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>HP-6900</t>
+          <t>EP-7743</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SN21882986</t>
+          <t>SN59518456</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1370.66</v>
+        <v>1359.23</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Retired</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
+          <t>In Repair</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>46017</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>Dell Support</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ITM0040</t>
+          <t>ITM0041</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Epson Monitor 40</t>
+          <t>Lenovo Monitor 41</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3357,54 +3139,48 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2025-03-27</t>
-        </is>
+          <t>Warehouse B</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>45586</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>EP-7743</t>
+          <t>LE-3947</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SN59518456</t>
+          <t>SN89225134</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1359.23</v>
+        <v>2000.54</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>45969</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Dell Support</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3416,137 +3192,125 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ITM0041</t>
+          <t>ITM0042</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lenovo Monitor 41</t>
+          <t>HP Router 42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Warehouse B</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2024-10-21</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2025-02-10</t>
-        </is>
+          <t>IT Closet</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>45548</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>LE-3947</t>
+          <t>HP-5749</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SN89225134</t>
+          <t>SN97132721</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>2000.54</v>
+        <v>1138.11</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2025-11-08</t>
-        </is>
+          <t>In Repair</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>46526</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>Dell Support</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ITM0042</t>
+          <t>ITM0043</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HP Router 42</t>
+          <t>Cisco Switch 43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>IT Closet</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2024-09-13</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2024-10-06</t>
-        </is>
+      <c r="F43" s="2" t="n">
+        <v>45630</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>HP-5749</t>
+          <t>CI-2101</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SN97132721</t>
+          <t>SN80779569</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1138.11</v>
+        <v>2051.57</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2027-05-19</t>
-        </is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>46520</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -3555,71 +3319,65 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ITM0043</t>
+          <t>ITM0044</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cisco Switch 43</t>
+          <t>HP Monitor 44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IT Closet</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2025-01-12</t>
-        </is>
+          <t>Remote Site</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>45488</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CI-2101</t>
+          <t>HP-1856</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SN80779569</t>
+          <t>SN37948014</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>2051.57</v>
+        <v>1478.12</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2027-05-13</t>
-        </is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>46422</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -3628,43 +3386,39 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ITM0044</t>
+          <t>ITM0045</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HP Monitor 44</t>
+          <t>HP Tablet 45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Remote Site</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2024-07-15</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2024-09-17</t>
-        </is>
+          <t>IT Closet</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>45410</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3673,99 +3427,91 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>HP-1856</t>
+          <t>HP-1464</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SN37948014</t>
+          <t>SN21109658</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1478.12</v>
+        <v>1435.13</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Retired</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2027-02-04</t>
-        </is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>45860</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Dell Support</t>
+          <t>AppleCare</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ITM0045</t>
+          <t>ITM0046</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HP Tablet 45</t>
+          <t>Epson Monitor 46</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IT Closet</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2024-05-02</t>
-        </is>
+          <t>Remote Site</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>45456</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>HP-1464</t>
+          <t>EP-9494</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SN21109658</t>
+          <t>SN35907638</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1435.13</v>
+        <v>1296.02</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2025-07-22</t>
-        </is>
+          <t>In Repair</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>46005</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -3774,144 +3520,132 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ITM0046</t>
+          <t>ITM0047</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Epson Monitor 46</t>
+          <t>HP Laptop 47</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>Remote Site</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2024-06-13</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2024-10-15</t>
-        </is>
+      <c r="F47" s="2" t="n">
+        <v>45313</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>EP-9494</t>
+          <t>HP-5704</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SN35907638</t>
+          <t>SN58436529</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1296.02</v>
+        <v>1739.37</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2025-12-14</t>
-        </is>
+      <c r="M47" s="2" t="n">
+        <v>46024</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>AppleCare</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ITM0047</t>
+          <t>ITM0048</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HP Laptop 47</t>
+          <t>Epson Router 48</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Remote Site</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2024-01-22</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2024-05-29</t>
-        </is>
+          <t>Warehouse A</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>45305</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>HP-5704</t>
+          <t>EP-6004</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SN58436529</t>
+          <t>SN96323811</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1739.37</v>
+        <v>2364.76</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2026-01-02</t>
-        </is>
+      <c r="M48" s="2" t="n">
+        <v>45687</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -3927,68 +3661,62 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ITM0048</t>
+          <t>ITM0049</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Epson Router 48</t>
+          <t>Apple Switch 49</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2024-01-14</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
+          <t>Remote Site</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>45617</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>EP-6004</t>
+          <t>AP-3044</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SN96323811</t>
+          <t>SN79460992</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>2364.76</v>
+        <v>2496.03</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>46455</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4000,12 +3728,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ITM0049</t>
+          <t>ITM0050</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Apple Switch 49</t>
+          <t>Apple Switch 50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4014,22 +3742,18 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Remote Site</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2024-11-21</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
+          <t>IT Closet</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>45354</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46091.63722909283</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -4038,26 +3762,24 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AP-3044</t>
+          <t>AP-1897</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>SN79460992</t>
+          <t>SN27693416</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>2496.03</v>
+        <v>117.4</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2027-03-09</t>
-        </is>
+          <t>In Repair</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>46376</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4065,79 +3787,6 @@
         </is>
       </c>
       <c r="O50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>ITM0050</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Apple Switch 50</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Switch</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>19</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>IT Closet</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2024-03-03</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2024-04-12</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>AP-1897</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>SN27693416</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>117.4</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>2026-12-20</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Cisco Warranty</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/data/inventory.xlsx
+++ b/data/inventory.xlsx
@@ -537,7 +537,7 @@
         <v>45634</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         <v>45539</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45542</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>45544</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>45559</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45525</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>45489</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>45538</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>45482</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>45357</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>45558</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45470</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45349</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45473</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>45327</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>45346</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>45423</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45347</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>45632</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45492</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45592</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45434</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45632</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45644</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>45443</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>45418</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>45321</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>45419</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>45293</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45416</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>45445</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45550</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45569</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>45363</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45354</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45343</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>45529</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>45345</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>45646</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>45586</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>45548</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>45630</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45488</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45410</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>45456</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45313</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>45305</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45617</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>45354</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46091.63722909283</v>
+        <v>46099.3835890687</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>

--- a/data/inventory.xlsx
+++ b/data/inventory.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,7 +517,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>changed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
         <v>45634</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -584,12 +584,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lenovo Laptop 3</t>
+          <t>hi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>again</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -604,7 +604,7 @@
         <v>45539</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lenovo Printer 4</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45542</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -726,9 +726,7 @@
           <t>Tablet</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>19</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Main Office</t>
@@ -738,7 +736,7 @@
         <v>45544</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -780,99 +778,99 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ITM0006</t>
+          <t>ITM0007</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cisco Printer 6</t>
+          <t>Dell Switch 7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Printer</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
+          <t>Remote Site</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45559</v>
+        <v>45525</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Dell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CI-6701</t>
+          <t>DE-2415</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SN12947104</t>
+          <t>SN87049713</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1687.5</v>
+        <v>2370.61</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>46071</v>
+        <v>46200</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Dell Support</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ITM0007</t>
+          <t>ITM0008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dell Switch 7</t>
+          <t>Dell Laptop 8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Remote Site</t>
+          <t>Warehouse A</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45525</v>
+        <v>45489</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -881,16 +879,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DE-2415</t>
+          <t>DE-1712</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>SN87049713</t>
+          <t>SN18103129</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2370.61</v>
+        <v>2180.61</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -898,28 +896,28 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>46200</v>
+        <v>46378</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>Lenovo Premium</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ITM0008</t>
+          <t>ITM0009</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dell Laptop 8</t>
+          <t>Lenovo Laptop 9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -928,141 +926,141 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
+          <t>Remote Site</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45489</v>
+        <v>45538</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Dell</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DE-1712</t>
+          <t>LE-1750</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>SN18103129</t>
+          <t>SN74709854</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2180.61</v>
+        <v>236.03</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>46378</v>
+        <v>46306</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Lenovo Premium</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ITM0009</t>
+          <t>ITM0010</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lenovo Laptop 9</t>
+          <t>Epson Switch 10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Remote Site</t>
+          <t>Main Office</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45538</v>
+        <v>45482</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LE-1750</t>
+          <t>EP-4082</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SN74709854</t>
+          <t>SN34126567</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>236.03</v>
+        <v>164.94</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>In Repair</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>46306</v>
+        <v>46095</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>Dell Support</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ITM0010</t>
+          <t>ITM0011</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Epson Switch 10</t>
+          <t>Cisco Tablet 11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1070,36 +1068,36 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45482</v>
+        <v>45357</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>EP-4082</t>
+          <t>CI-2186</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>SN34126567</t>
+          <t>SN68308926</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>164.94</v>
+        <v>1459.56</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>In Repair</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>46095</v>
+        <v>45811</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1115,62 +1113,62 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ITM0011</t>
+          <t>ITM0012</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cisco Tablet 11</t>
+          <t>Epson Laptop 12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Main Office</t>
+          <t>Warehouse A</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45357</v>
+        <v>45558</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CI-2186</t>
+          <t>EP-7148</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SN68308926</t>
+          <t>SN46504782</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1459.56</v>
+        <v>436.06</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>45811</v>
+        <v>46076</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Dell Support</t>
+          <t>AppleCare</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1182,50 +1180,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ITM0012</t>
+          <t>ITM0013</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Epson Laptop 12</t>
+          <t>Cisco Switch 13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
+          <t>Warehouse B</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45558</v>
+        <v>45470</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EP-7148</t>
+          <t>CI-2801</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>SN46504782</t>
+          <t>SN53129241</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>436.06</v>
+        <v>373.47</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1233,78 +1231,78 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>46076</v>
+        <v>46484</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>AppleCare</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ITM0013</t>
+          <t>ITM0014</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cisco Switch 13</t>
+          <t>Epson Laptop 14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Warehouse B</t>
+          <t>Warehouse A</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45470</v>
+        <v>45349</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CI-2801</t>
+          <t>EP-5617</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>SN53129241</t>
+          <t>SN55743232</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>373.47</v>
+        <v>735.75</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>46484</v>
+        <v>46372</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>Dell Support</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1316,21 +1314,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ITM0014</t>
+          <t>ITM0015</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Epson Laptop 14</t>
+          <t>Cisco Tablet 15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1338,36 +1336,36 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45349</v>
+        <v>45473</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EP-5617</t>
+          <t>CI-2377</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SN55743232</t>
+          <t>SN20908357</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>735.75</v>
+        <v>1139.36</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>In Repair</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>46372</v>
+        <v>45876</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1376,95 +1374,95 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ITM0015</t>
+          <t>ITM0016</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cisco Tablet 15</t>
+          <t>Lenovo Switch 16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
+          <t>Remote Site</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45473</v>
+        <v>45327</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CI-2377</t>
+          <t>LE-4738</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SN20908357</t>
+          <t>SN48992827</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1139.36</v>
+        <v>1092.84</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>In Repair</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>45876</v>
+        <v>45963</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Dell Support</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ITM0016</t>
+          <t>ITM0017</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lenovo Switch 16</t>
+          <t>Apple Laptop 17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1472,36 +1470,36 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45327</v>
+        <v>45346</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LE-4738</t>
+          <t>AP-7166</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>SN48992827</t>
+          <t>SN96842624</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1092.84</v>
+        <v>474.43</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>In Repair</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>45963</v>
+        <v>46011</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1510,57 +1508,57 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ITM0017</t>
+          <t>ITM0018</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Apple Laptop 17</t>
+          <t>Cisco Printer 18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Remote Site</t>
+          <t>Warehouse A</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45346</v>
+        <v>45423</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AP-7166</t>
+          <t>CI-5274</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>SN96842624</t>
+          <t>SN32000764</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>474.43</v>
+        <v>2180.93</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1568,74 +1566,74 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>46011</v>
+        <v>45901</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>AppleCare</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ITM0018</t>
+          <t>ITM0019</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cisco Printer 18</t>
+          <t>Epson Switch 19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Printer</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
+          <t>Warehouse B</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45423</v>
+        <v>45347</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CI-5274</t>
+          <t>EP-9652</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SN32000764</t>
+          <t>SN57657634</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2180.93</v>
+        <v>557.09</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>In Repair</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>45901</v>
+        <v>46137</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1651,17 +1649,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ITM0019</t>
+          <t>ITM0020</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Epson Switch 19</t>
+          <t>Epson Monitor 20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1669,14 +1667,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Warehouse B</t>
+          <t>Main Office</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45347</v>
+        <v>45632</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1685,24 +1683,24 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>EP-9652</t>
+          <t>EP-3391</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SN57657634</t>
+          <t>SN80990521</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>557.09</v>
+        <v>1575.15</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>46137</v>
+        <v>46267</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1711,69 +1709,69 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ITM0020</t>
+          <t>ITM0021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Epson Monitor 20</t>
+          <t>Apple Laptop 21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Main Office</t>
+          <t>IT Closet</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45632</v>
+        <v>45492</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>EP-3391</t>
+          <t>AP-6473</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SN80990521</t>
+          <t>SN43317146</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1575.15</v>
+        <v>2389.73</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>In Repair</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>46267</v>
+        <v>45897</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>AppleCare</t>
+          <t>Lenovo Premium</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1785,129 +1783,129 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ITM0021</t>
+          <t>ITM0022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Apple Laptop 21</t>
+          <t>Dell Printer 22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IT Closet</t>
+          <t>Remote Site</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45492</v>
+        <v>45592</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Dell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AP-6473</t>
+          <t>DE-4929</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SN43317146</t>
+          <t>SN87250266</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>2389.73</v>
+        <v>997.01</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>In Repair</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>45897</v>
+        <v>46371</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Lenovo Premium</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ITM0022</t>
+          <t>ITM0023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dell Printer 22</t>
+          <t>Apple Switch 23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Printer</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Remote Site</t>
+          <t>Warehouse A</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45592</v>
+        <v>45434</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Dell</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DE-4929</t>
+          <t>AP-9603</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SN87250266</t>
+          <t>SN95175226</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>997.01</v>
+        <v>661.0599999999999</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>46371</v>
+        <v>46449</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>AppleCare</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1919,21 +1917,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ITM0023</t>
+          <t>ITM0024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apple Switch 23</t>
+          <t>Apple Tablet 24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1941,10 +1939,10 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45434</v>
+        <v>45632</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1953,28 +1951,28 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AP-9603</t>
+          <t>AP-7433</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>SN95175226</t>
+          <t>SN76849184</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>661.0599999999999</v>
+        <v>1246.48</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>In Repair</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>46449</v>
+        <v>46662</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>AppleCare</t>
+          <t>Dell Support</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1986,62 +1984,62 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ITM0024</t>
+          <t>ITM0025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Apple Tablet 24</t>
+          <t>Epson Switch 25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
+          <t>IT Closet</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45632</v>
+        <v>45644</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AP-7433</t>
+          <t>EP-4607</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SN76849184</t>
+          <t>SN31564647</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1246.48</v>
+        <v>1661.51</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>In Repair</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>46662</v>
+        <v>46089</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Dell Support</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2053,12 +2051,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ITM0025</t>
+          <t>ITM0026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Epson Switch 25</t>
+          <t>Epson Switch 26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2067,18 +2065,18 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IT Closet</t>
+          <t>Warehouse A</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45644</v>
+        <v>45443</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2087,28 +2085,28 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>EP-4607</t>
+          <t>EP-9269</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SN31564647</t>
+          <t>SN21333025</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1661.51</v>
+        <v>2350.61</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>46089</v>
+        <v>46080</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>AppleCare</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2120,88 +2118,88 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ITM0026</t>
+          <t>ITM0027</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Epson Switch 26</t>
+          <t>Dell Router 27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
+          <t>Main Office</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45443</v>
+        <v>45418</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Dell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>EP-9269</t>
+          <t>DE-1340</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SN21333025</t>
+          <t>SN27521419</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2350.61</v>
+        <v>2205.55</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>In Repair</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>46080</v>
+        <v>45947</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>AppleCare</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ITM0027</t>
+          <t>ITM0028</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dell Router 27</t>
+          <t>Epson Laptop 28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2209,77 +2207,77 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45418</v>
+        <v>45321</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Dell</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>DE-1340</t>
+          <t>EP-9395</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>SN27521419</t>
+          <t>SN97552808</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2205.55</v>
+        <v>2482.81</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>In Repair</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>45947</v>
+        <v>46070</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>Dell Support</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ITM0028</t>
+          <t>ITM0029</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Epson Laptop 28</t>
+          <t>Epson Tablet 29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Main Office</t>
+          <t>IT Closet</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45321</v>
+        <v>45419</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2288,28 +2286,28 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>EP-9395</t>
+          <t>EP-1066</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SN97552808</t>
+          <t>SN93333985</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>2482.81</v>
+        <v>950.09</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>In Repair</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>46070</v>
+        <v>45832</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Dell Support</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2321,21 +2319,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ITM0029</t>
+          <t>ITM0030</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Epson Tablet 29</t>
+          <t>HP Laptop 30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2343,28 +2341,28 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45419</v>
+        <v>45293</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>EP-1066</t>
+          <t>HP-4733</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SN93333985</t>
+          <t>SN34742385</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>950.09</v>
+        <v>2499.3</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2372,7 +2370,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>45832</v>
+        <v>45875</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2381,24 +2379,24 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ITM0030</t>
+          <t>ITM0031</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HP Laptop 30</t>
+          <t>HP Router 31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -2410,10 +2408,10 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45293</v>
+        <v>45416</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2422,16 +2420,16 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>HP-4733</t>
+          <t>HP-8118</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SN34742385</t>
+          <t>SN69731506</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>2499.3</v>
+        <v>166.49</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2439,11 +2437,11 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>45875</v>
+        <v>46282</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>Lenovo Premium</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2455,50 +2453,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ITM0031</t>
+          <t>ITM0032</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HP Router 31</t>
+          <t>Epson Laptop 32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IT Closet</t>
+          <t>Warehouse B</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45416</v>
+        <v>45445</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>HP-8118</t>
+          <t>EP-6464</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>SN69731506</t>
+          <t>SN29099365</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>166.49</v>
+        <v>1136.78</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2506,7 +2504,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>46282</v>
+        <v>46024</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2515,28 +2513,28 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ITM0032</t>
+          <t>ITM0033</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Epson Laptop 32</t>
+          <t>Dell Printer 33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Printer</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2544,40 +2542,40 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45445</v>
+        <v>45550</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Dell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>EP-6464</t>
+          <t>DE-1295</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>SN29099365</t>
+          <t>SN68145944</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1136.78</v>
+        <v>408.32</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>In Repair</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>46024</v>
+        <v>46031</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Lenovo Premium</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2589,21 +2587,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ITM0033</t>
+          <t>ITM0034</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dell Printer 33</t>
+          <t>Epson Monitor 34</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Printer</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2611,28 +2609,28 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45550</v>
+        <v>45569</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Dell</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>DE-1295</t>
+          <t>EP-5669</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>SN68145944</t>
+          <t>SN26610527</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>408.32</v>
+        <v>1599.97</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2640,11 +2638,11 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>46031</v>
+        <v>46114</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2656,79 +2654,79 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ITM0034</t>
+          <t>ITM0035</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Epson Monitor 34</t>
+          <t>Cisco Switch 35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Warehouse B</t>
+          <t>Warehouse A</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45569</v>
+        <v>45363</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>EP-5669</t>
+          <t>CI-6537</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>SN26610527</t>
+          <t>SN80427769</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1599.97</v>
+        <v>1109.75</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>46114</v>
+        <v>45976</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>Lenovo Premium</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ITM0035</t>
+          <t>ITM0036</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cisco Switch 35</t>
+          <t>Epson Switch 36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2737,7 +2735,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2745,40 +2743,40 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45363</v>
+        <v>45354</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CI-6537</t>
+          <t>EP-1758</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>SN80427769</t>
+          <t>SN53690854</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1109.75</v>
+        <v>2216.96</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>In Repair</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>45976</v>
+        <v>45776</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Lenovo Premium</t>
+          <t>AppleCare</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2790,62 +2788,62 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ITM0036</t>
+          <t>ITM0037</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Epson Switch 36</t>
+          <t>Apple Monitor 37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
+          <t>Remote Site</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45354</v>
+        <v>45343</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>EP-1758</t>
+          <t>AP-9201</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>SN53690854</t>
+          <t>SN54771677</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>2216.96</v>
+        <v>1068.81</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>In Repair</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>45776</v>
+        <v>45840</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>AppleCare</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2857,62 +2855,62 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ITM0037</t>
+          <t>ITM0038</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Apple Monitor 37</t>
+          <t>Epson Router 38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Remote Site</t>
+          <t>IT Closet</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45343</v>
+        <v>45529</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AP-9201</t>
+          <t>EP-7936</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SN54771677</t>
+          <t>SN38050053</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1068.81</v>
+        <v>511.93</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>In Repair</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>45840</v>
+        <v>46438</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2924,62 +2922,62 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ITM0038</t>
+          <t>ITM0039</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Epson Router 38</t>
+          <t>HP Monitor 39</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IT Closet</t>
+          <t>Remote Site</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45529</v>
+        <v>45345</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>EP-7936</t>
+          <t>HP-6900</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SN38050053</t>
+          <t>SN21882986</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>511.93</v>
+        <v>1370.66</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>In Repair</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>46438</v>
+        <v>45947</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2991,12 +2989,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ITM0039</t>
+          <t>ITM0040</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HP Monitor 39</t>
+          <t>Epson Monitor 40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3005,65 +3003,65 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Remote Site</t>
+          <t>Warehouse A</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45345</v>
+        <v>45646</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>HP-6900</t>
+          <t>EP-7743</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SN21882986</t>
+          <t>SN59518456</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1370.66</v>
+        <v>1359.23</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>In Repair</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>45947</v>
+        <v>46017</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>Dell Support</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ITM0040</t>
+          <t>ITM0041</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Epson Monitor 40</t>
+          <t>Lenovo Monitor 41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3072,48 +3070,48 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
+          <t>Warehouse B</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45646</v>
+        <v>45586</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>EP-7743</t>
+          <t>LE-3947</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SN59518456</t>
+          <t>SN89225134</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1359.23</v>
+        <v>2000.54</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>In Repair</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>46017</v>
+        <v>45969</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Dell Support</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3125,88 +3123,88 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ITM0041</t>
+          <t>ITM0042</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lenovo Monitor 41</t>
+          <t>HP Router 42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Warehouse B</t>
+          <t>IT Closet</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45586</v>
+        <v>45548</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LE-3947</t>
+          <t>HP-5749</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SN89225134</t>
+          <t>SN97132721</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>2000.54</v>
+        <v>1138.11</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>In Repair</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>45969</v>
+        <v>46526</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Cisco Warranty</t>
+          <t>Dell Support</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ITM0042</t>
+          <t>ITM0043</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HP Router 42</t>
+          <t>Cisco Switch 43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -3214,36 +3212,36 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45548</v>
+        <v>45630</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>HP-5749</t>
+          <t>CI-2101</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SN97132721</t>
+          <t>SN80779569</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1138.11</v>
+        <v>2051.57</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>In Repair</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>46526</v>
+        <v>46520</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -3252,65 +3250,65 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ITM0043</t>
+          <t>ITM0044</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cisco Switch 43</t>
+          <t>HP Monitor 44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IT Closet</t>
+          <t>Remote Site</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45630</v>
+        <v>45488</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CI-2101</t>
+          <t>HP-1856</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SN80779569</t>
+          <t>SN37948014</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>2051.57</v>
+        <v>1478.12</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>46520</v>
+        <v>46422</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -3319,39 +3317,39 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ITM0044</t>
+          <t>ITM0045</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HP Monitor 44</t>
+          <t>HP Tablet 45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Remote Site</t>
+          <t>IT Closet</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45488</v>
+        <v>45410</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3360,91 +3358,91 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>HP-1856</t>
+          <t>HP-1464</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SN37948014</t>
+          <t>SN21109658</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1478.12</v>
+        <v>1435.13</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>46422</v>
+        <v>45860</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Dell Support</t>
+          <t>AppleCare</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ITM0045</t>
+          <t>ITM0046</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HP Tablet 45</t>
+          <t>Epson Monitor 46</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IT Closet</t>
+          <t>Remote Site</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45410</v>
+        <v>45456</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>HP-1464</t>
+          <t>EP-9494</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SN21109658</t>
+          <t>SN35907638</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1435.13</v>
+        <v>1296.02</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>In Repair</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>45860</v>
+        <v>46005</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -3453,28 +3451,28 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ITM0046</t>
+          <t>ITM0047</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Epson Monitor 46</t>
+          <t>HP Laptop 47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -3482,28 +3480,28 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45456</v>
+        <v>45313</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>EP-9494</t>
+          <t>HP-5704</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SN35907638</t>
+          <t>SN58436529</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1296.02</v>
+        <v>1739.37</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3511,66 +3509,66 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>46005</v>
+        <v>46024</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>AppleCare</t>
+          <t>HP Care</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ITM0047</t>
+          <t>ITM0048</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HP Laptop 47</t>
+          <t>Epson Router 48</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Router</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Remote Site</t>
+          <t>Warehouse A</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45313</v>
+        <v>45305</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Epson</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>HP-5704</t>
+          <t>EP-6004</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SN58436529</t>
+          <t>SN96323811</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1739.37</v>
+        <v>2364.76</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3578,7 +3576,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>46024</v>
+        <v>45687</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -3594,62 +3592,62 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ITM0048</t>
+          <t>ITM0049</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Epson Router 48</t>
+          <t>Apple Switch 49</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Switch</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Warehouse A</t>
+          <t>Remote Site</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45305</v>
+        <v>45617</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Epson</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>EP-6004</t>
+          <t>AP-3044</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>SN96323811</t>
+          <t>SN79460992</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>2364.76</v>
+        <v>2496.03</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>In Repair</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>45687</v>
+        <v>46455</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>HP Care</t>
+          <t>Cisco Warranty</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3661,12 +3659,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ITM0049</t>
+          <t>ITM0050</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Apple Switch 49</t>
+          <t>Apple Switch 50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3675,18 +3673,18 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Remote Site</t>
+          <t>IT Closet</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45617</v>
+        <v>45354</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46099.3835890687</v>
+        <v>46106.57403869061</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3695,24 +3693,24 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AP-3044</t>
+          <t>AP-1897</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SN79460992</t>
+          <t>SN27693416</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>2496.03</v>
+        <v>117.4</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>In Repair</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>46455</v>
+        <v>46376</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -3720,73 +3718,6 @@
         </is>
       </c>
       <c r="O49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>ITM0050</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Apple Switch 50</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Switch</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>19</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>IT Closet</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>45354</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>46099.3835890687</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>AP-1897</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>SN27693416</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>117.4</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>In Repair</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>46376</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Cisco Warranty</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>

--- a/data/inventory.xlsx
+++ b/data/inventory.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,50 +460,55 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>DateAdded</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>LastUpdated</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ModelNumber</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>SerialNumber</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>WarrantyExpiration</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>WarrantyProvider</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>AlertSent</t>
         </is>
@@ -533,44 +538,49 @@
           <t>Main Office</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>45634</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>25568.70886150463</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Lenovo</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>LE-5369</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>SN94784503</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1435.87</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n">
-        <v>46223</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="2" t="n">
+        <v>25568.70886832176</v>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>Dell Support</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -600,44 +610,45 @@
           <t>Warehouse B</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>45539</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>25568.70886040509</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Lenovo</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>LE-7685</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>SN97026474</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>1568.69</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n">
-        <v>46367</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="n">
+        <v>25568.70886998843</v>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>HP Care</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -667,44 +678,45 @@
           <t>Warehouse B</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>45542</v>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>25568.70886043982</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Lenovo</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>LE-1836</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>SN13646074</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>2408.84</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n">
-        <v>46072</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="2" t="n">
+        <v>25568.70886657407</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>Cisco Warranty</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -718,7 +730,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cisco Tablet 5</t>
+          <t>wewew</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -732,44 +744,45 @@
           <t>Main Office</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>45544</v>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>25568.70886046296</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Cisco</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>CI-2350</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>SN69836053</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>313.09</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n">
-        <v>45945</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="2" t="n">
+        <v>25568.70886510417</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>AppleCare</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -799,44 +812,45 @@
           <t>Remote Site</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>45525</v>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>25568.70886024306</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Dell</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>DE-2415</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>SN87049713</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2370.61</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n">
-        <v>46200</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="2" t="n">
+        <v>25568.70886805556</v>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>Cisco Warranty</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -845,7 +859,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ITM0008</t>
+          <t>wewe</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -866,44 +880,45 @@
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>45489</v>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>25568.70885982639</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Dell</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>DE-1712</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>SN18103129</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>2180.61</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n">
-        <v>46378</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="2" t="n">
+        <v>25568.70887011574</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>Lenovo Premium</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -933,44 +948,45 @@
           <t>Remote Site</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>45538</v>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>25568.70886039352</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Lenovo</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>LE-1750</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>SN74709854</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>236.03</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M8" s="2" t="n">
-        <v>46306</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="2" t="n">
+        <v>25568.70886928241</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>Cisco Warranty</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1000,44 +1016,45 @@
           <t>Main Office</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
-        <v>45482</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>25568.70885974537</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>EP-4082</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>SN34126567</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>164.94</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="2" t="n">
+        <v>25568.70886684028</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>Dell Support</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1067,44 +1084,45 @@
           <t>Main Office</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>45357</v>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>25568.70885829861</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Cisco</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>CI-2186</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>SN68308926</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>1459.56</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
-        <v>45811</v>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="2" t="n">
+        <v>25568.70886355324</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>Dell Support</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1134,44 +1152,49 @@
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
-        <v>45558</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>25568.708860625</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>EP-7148</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>SN46504782</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>436.06</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n">
-        <v>46076</v>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="2" t="n">
+        <v>25568.70886662037</v>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>AppleCare</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1201,44 +1224,45 @@
           <t>Warehouse B</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
-        <v>45470</v>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>25568.70885960648</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Cisco</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>CI-2801</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>SN53129241</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>373.47</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M12" s="2" t="n">
-        <v>46484</v>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="2" t="n">
+        <v>25568.70887134259</v>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>Cisco Warranty</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1268,44 +1292,45 @@
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>45349</v>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>25568.70885820602</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>EP-5617</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>SN55743232</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>735.75</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n">
-        <v>46372</v>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="2" t="n">
+        <v>25568.7088700463</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>Dell Support</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1335,44 +1360,45 @@
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>45473</v>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>25568.7088596412</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Cisco</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>CI-2377</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>SN20908357</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>1139.36</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M14" s="2" t="n">
-        <v>45876</v>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="N14" s="2" t="n">
+        <v>25568.70886430555</v>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>Dell Support</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1402,44 +1428,45 @@
           <t>Remote Site</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
-        <v>45327</v>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>25568.70885795139</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Lenovo</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>LE-4738</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>SN48992827</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>1092.84</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M15" s="2" t="n">
-        <v>45963</v>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" s="2" t="n">
+        <v>25568.7088653125</v>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>HP Care</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1469,44 +1496,45 @@
           <t>Remote Site</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
-        <v>45346</v>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>25568.7088581713</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>AP-7166</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>SN96842624</t>
         </is>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>474.43</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M16" s="2" t="n">
-        <v>46011</v>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="2" t="n">
+        <v>25568.70886586805</v>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>HP Care</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1536,44 +1564,45 @@
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
-        <v>45423</v>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>25568.7088590625</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Cisco</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>CI-5274</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>SN32000764</t>
         </is>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>2180.93</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M17" s="2" t="n">
-        <v>45901</v>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="2" t="n">
+        <v>25568.70886459491</v>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>AppleCare</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1603,44 +1632,45 @@
           <t>Warehouse B</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
-        <v>45347</v>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>25568.70885818287</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>EP-9652</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>SN57657634</t>
         </is>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>557.09</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M18" s="2" t="n">
-        <v>46137</v>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="2" t="n">
+        <v>25568.70886732639</v>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>AppleCare</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1670,44 +1700,45 @@
           <t>Main Office</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
-        <v>45632</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>25568.70886148148</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>EP-3391</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>SN80990521</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1575.15</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M19" s="2" t="n">
-        <v>46267</v>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" s="2" t="n">
+        <v>25568.70886883102</v>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>AppleCare</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1737,44 +1768,45 @@
           <t>IT Closet</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
-        <v>45492</v>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>25568.70885986111</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>AP-6473</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>SN43317146</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>2389.73</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M20" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" s="2" t="n">
+        <v>25568.70886454861</v>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>Lenovo Premium</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1804,44 +1836,45 @@
           <t>Remote Site</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
-        <v>45592</v>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>25568.70886101852</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>Dell</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>DE-4929</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>SN87250266</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>997.01</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M21" s="2" t="n">
-        <v>46371</v>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" s="2" t="n">
+        <v>25568.70887003472</v>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>Cisco Warranty</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1871,44 +1904,45 @@
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
-        <v>45434</v>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H22" t="inlineStr">
+        <v>25568.70885918981</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>AP-9603</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>SN95175226</t>
         </is>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>661.0599999999999</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M22" s="2" t="n">
-        <v>46449</v>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" s="2" t="n">
+        <v>25568.7088709375</v>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>AppleCare</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1938,44 +1972,45 @@
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n">
-        <v>45632</v>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H23" t="inlineStr">
+        <v>25568.70886148148</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>AP-7433</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>SN76849184</t>
         </is>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>1246.48</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M23" s="2" t="n">
-        <v>46662</v>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="N23" s="2" t="n">
+        <v>25568.70887340278</v>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>Dell Support</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2005,44 +2040,45 @@
           <t>IT Closet</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
-        <v>45644</v>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H24" t="inlineStr">
+        <v>25568.70886162037</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>EP-4607</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>SN31564647</t>
         </is>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>1661.51</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M24" s="2" t="n">
-        <v>46089</v>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="N24" s="2" t="n">
+        <v>25568.70886677083</v>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>HP Care</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2072,44 +2108,45 @@
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n">
-        <v>45443</v>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H25" t="inlineStr">
+        <v>25568.70885929398</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>EP-9269</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>SN21333025</t>
         </is>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>2350.61</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M25" s="2" t="n">
-        <v>46080</v>
-      </c>
-      <c r="N25" t="inlineStr">
+      <c r="N25" s="2" t="n">
+        <v>25568.70886666667</v>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>AppleCare</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2139,44 +2176,45 @@
           <t>Main Office</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
-        <v>45418</v>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H26" t="inlineStr">
+        <v>25568.70885900463</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>Dell</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>DE-1340</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>SN27521419</t>
         </is>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>2205.55</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M26" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="N26" t="inlineStr">
+      <c r="N26" s="2" t="n">
+        <v>25568.70886512732</v>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>HP Care</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2206,44 +2244,45 @@
           <t>Main Office</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n">
-        <v>45321</v>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H27" t="inlineStr">
+        <v>25568.70885788195</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>EP-9395</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>SN97552808</t>
         </is>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2482.81</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M27" s="2" t="n">
-        <v>46070</v>
-      </c>
-      <c r="N27" t="inlineStr">
+      <c r="N27" s="2" t="n">
+        <v>25568.70886655093</v>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>Dell Support</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2273,44 +2312,45 @@
           <t>IT Closet</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
-        <v>45419</v>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H28" t="inlineStr">
+        <v>25568.7088590162</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>EP-1066</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>SN93333985</t>
         </is>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>950.09</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M28" s="2" t="n">
-        <v>45832</v>
-      </c>
-      <c r="N28" t="inlineStr">
+      <c r="N28" s="2" t="n">
+        <v>25568.7088637963</v>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>HP Care</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2340,44 +2380,45 @@
           <t>IT Closet</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n">
-        <v>45293</v>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H29" t="inlineStr">
+        <v>25568.70885755787</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>HP-4733</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>SN34742385</t>
         </is>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>2499.3</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M29" s="2" t="n">
-        <v>45875</v>
-      </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="2" t="n">
+        <v>25568.70886429398</v>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>HP Care</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2407,44 +2448,45 @@
           <t>IT Closet</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n">
-        <v>45416</v>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H30" t="inlineStr">
+        <v>25568.70885898148</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>HP-8118</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>SN69731506</t>
         </is>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>166.49</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M30" s="2" t="n">
-        <v>46282</v>
-      </c>
-      <c r="N30" t="inlineStr">
+      <c r="N30" s="2" t="n">
+        <v>25568.70886900463</v>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>Lenovo Premium</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2474,44 +2516,45 @@
           <t>Warehouse B</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n">
-        <v>45445</v>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H31" t="inlineStr">
+        <v>25568.70885931713</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>EP-6464</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>SN29099365</t>
         </is>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>1136.78</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M31" s="2" t="n">
-        <v>46024</v>
-      </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" s="2" t="n">
+        <v>25568.70886601852</v>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>Lenovo Premium</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2541,44 +2584,45 @@
           <t>Warehouse B</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n">
-        <v>45550</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H32" t="inlineStr">
+        <v>25568.70886053241</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>Dell</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>DE-1295</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>SN68145944</t>
         </is>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>408.32</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M32" s="2" t="n">
-        <v>46031</v>
-      </c>
-      <c r="N32" t="inlineStr">
+      <c r="N32" s="2" t="n">
+        <v>25568.70886609954</v>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>Cisco Warranty</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2608,44 +2652,45 @@
           <t>Warehouse B</t>
         </is>
       </c>
-      <c r="F33" s="2" t="n">
-        <v>45569</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H33" t="inlineStr">
+        <v>25568.70886075231</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>EP-5669</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>SN26610527</t>
         </is>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>1599.97</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M33" s="2" t="n">
-        <v>46114</v>
-      </c>
-      <c r="N33" t="inlineStr">
+      <c r="N33" s="2" t="n">
+        <v>25568.70886706018</v>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>HP Care</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2675,44 +2720,45 @@
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n">
-        <v>45363</v>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H34" t="inlineStr">
+        <v>25568.70885836806</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>Cisco</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>CI-6537</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>SN80427769</t>
         </is>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>1109.75</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M34" s="2" t="n">
-        <v>45976</v>
-      </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="2" t="n">
+        <v>25568.70886546296</v>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>Lenovo Premium</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2742,44 +2788,45 @@
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n">
-        <v>45354</v>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H35" t="inlineStr">
+        <v>25568.70885826389</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>EP-1758</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>SN53690854</t>
         </is>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2216.96</v>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M35" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="N35" t="inlineStr">
+      <c r="N35" s="2" t="n">
+        <v>25568.70886314815</v>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>AppleCare</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2809,44 +2856,45 @@
           <t>Remote Site</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n">
-        <v>45343</v>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H36" t="inlineStr">
+        <v>25568.70885813658</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>AP-9201</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>SN54771677</t>
         </is>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>1068.81</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M36" s="2" t="n">
-        <v>45840</v>
-      </c>
-      <c r="N36" t="inlineStr">
+      <c r="N36" s="2" t="n">
+        <v>25568.70886388889</v>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>Cisco Warranty</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2876,44 +2924,45 @@
           <t>IT Closet</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n">
-        <v>45529</v>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H37" t="inlineStr">
+        <v>25568.70886028935</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>EP-7936</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>SN38050053</t>
         </is>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>511.93</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M37" s="2" t="n">
-        <v>46438</v>
-      </c>
-      <c r="N37" t="inlineStr">
+      <c r="N37" s="2" t="n">
+        <v>25568.70887081018</v>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>HP Care</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2943,44 +2992,45 @@
           <t>Remote Site</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n">
-        <v>45345</v>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H38" t="inlineStr">
+        <v>25568.70885815972</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>HP-6900</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>SN21882986</t>
         </is>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>1370.66</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M38" s="2" t="n">
-        <v>45947</v>
-      </c>
-      <c r="N38" t="inlineStr">
+      <c r="N38" s="2" t="n">
+        <v>25568.70886512732</v>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>Cisco Warranty</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3010,44 +3060,45 @@
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n">
-        <v>45646</v>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H39" t="inlineStr">
+        <v>25568.70886164352</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>EP-7743</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>SN59518456</t>
         </is>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>1359.23</v>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M39" s="2" t="n">
-        <v>46017</v>
-      </c>
-      <c r="N39" t="inlineStr">
+      <c r="N39" s="2" t="n">
+        <v>25568.7088659375</v>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>Dell Support</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3077,44 +3128,45 @@
           <t>Warehouse B</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n">
-        <v>45586</v>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H40" t="inlineStr">
+        <v>25568.70886094907</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>Lenovo</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>LE-3947</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>SN89225134</t>
         </is>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>2000.54</v>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M40" s="2" t="n">
-        <v>45969</v>
-      </c>
-      <c r="N40" t="inlineStr">
+      <c r="N40" s="2" t="n">
+        <v>25568.70886538194</v>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>Cisco Warranty</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3144,44 +3196,45 @@
           <t>IT Closet</t>
         </is>
       </c>
-      <c r="F41" s="2" t="n">
-        <v>45548</v>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H41" t="inlineStr">
+        <v>25568.70886050926</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>HP-5749</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>SN97132721</t>
         </is>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1138.11</v>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M41" s="2" t="n">
-        <v>46526</v>
-      </c>
-      <c r="N41" t="inlineStr">
+      <c r="N41" s="2" t="n">
+        <v>25568.70887182871</v>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>Dell Support</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3211,44 +3264,45 @@
           <t>IT Closet</t>
         </is>
       </c>
-      <c r="F42" s="2" t="n">
-        <v>45630</v>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H42" t="inlineStr">
+        <v>25568.70886145833</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>Cisco</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>CI-2101</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>SN80779569</t>
         </is>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>2051.57</v>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M42" s="2" t="n">
-        <v>46520</v>
-      </c>
-      <c r="N42" t="inlineStr">
+      <c r="N42" s="2" t="n">
+        <v>25568.70887175926</v>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>Dell Support</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3278,44 +3332,45 @@
           <t>Remote Site</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n">
-        <v>45488</v>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H43" t="inlineStr">
+        <v>25568.70885981481</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>HP-1856</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>SN37948014</t>
         </is>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>1478.12</v>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Retired</t>
         </is>
       </c>
-      <c r="M43" s="2" t="n">
-        <v>46422</v>
-      </c>
-      <c r="N43" t="inlineStr">
+      <c r="N43" s="2" t="n">
+        <v>25568.708870625</v>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>Dell Support</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3345,44 +3400,45 @@
           <t>IT Closet</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n">
-        <v>45410</v>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H44" t="inlineStr">
+        <v>25568.70885891204</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>HP-1464</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>SN21109658</t>
         </is>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>1435.13</v>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M44" s="2" t="n">
-        <v>45860</v>
-      </c>
-      <c r="N44" t="inlineStr">
+      <c r="N44" s="2" t="n">
+        <v>25568.70886412037</v>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>AppleCare</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3412,44 +3468,45 @@
           <t>Remote Site</t>
         </is>
       </c>
-      <c r="F45" s="2" t="n">
-        <v>45456</v>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H45" t="inlineStr">
+        <v>25568.70885944444</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>EP-9494</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>SN35907638</t>
         </is>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>1296.02</v>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M45" s="2" t="n">
-        <v>46005</v>
-      </c>
-      <c r="N45" t="inlineStr">
+      <c r="N45" s="2" t="n">
+        <v>25568.70886579861</v>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>AppleCare</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3479,44 +3536,45 @@
           <t>Remote Site</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n">
-        <v>45313</v>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H46" t="inlineStr">
+        <v>25568.70885778935</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>HP-5704</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>SN58436529</t>
         </is>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>1739.37</v>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M46" s="2" t="n">
-        <v>46024</v>
-      </c>
-      <c r="N46" t="inlineStr">
+      <c r="N46" s="2" t="n">
+        <v>25568.70886601852</v>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>HP Care</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3546,44 +3604,45 @@
           <t>Warehouse A</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n">
-        <v>45305</v>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H47" t="inlineStr">
+        <v>25568.70885769676</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>Epson</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>EP-6004</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>SN96323811</t>
         </is>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>2364.76</v>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M47" s="2" t="n">
-        <v>45687</v>
-      </c>
-      <c r="N47" t="inlineStr">
+      <c r="N47" s="2" t="n">
+        <v>25568.70886211806</v>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>HP Care</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3613,44 +3672,45 @@
           <t>Remote Site</t>
         </is>
       </c>
-      <c r="F48" s="2" t="n">
-        <v>45617</v>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H48" t="inlineStr">
+        <v>25568.70886130787</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I48" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>AP-3044</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>SN79460992</t>
         </is>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>2496.03</v>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="M48" s="2" t="n">
-        <v>46455</v>
-      </c>
-      <c r="N48" t="inlineStr">
+      <c r="N48" s="2" t="n">
+        <v>25568.70887100694</v>
+      </c>
+      <c r="O48" t="inlineStr">
         <is>
           <t>Cisco Warranty</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3680,48 +3740,87 @@
           <t>IT Closet</t>
         </is>
       </c>
-      <c r="F49" s="2" t="n">
-        <v>45354</v>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" s="2" t="n">
-        <v>46106.57403869061</v>
-      </c>
-      <c r="H49" t="inlineStr">
+        <v>25568.70885826389</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>AP-1897</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>SN27693416</t>
         </is>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>117.4</v>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>In Repair</t>
         </is>
       </c>
-      <c r="M49" s="2" t="n">
-        <v>46376</v>
-      </c>
-      <c r="N49" t="inlineStr">
+      <c r="N49" s="2" t="n">
+        <v>25568.70887009259</v>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>Cisco Warranty</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ITM0051</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Chess Board</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" s="2" t="n">
+        <v>46168.589347056</v>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
